--- a/calendar_chilean_2023B.xlsx
+++ b/calendar_chilean_2023B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C369A2-3883-5F4B-A021-D087293A5684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD19761-A7FB-4147-8F44-DD8BF71DD201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25740" yWindow="580" windowWidth="25080" windowHeight="20840" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
+    <workbookView xWindow="16260" yWindow="500" windowWidth="20860" windowHeight="21100" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -137,6 +137,12 @@
   </si>
   <si>
     <t>wheather loss</t>
+  </si>
+  <si>
+    <t>31/61</t>
+  </si>
+  <si>
+    <t>pb telescope</t>
   </si>
 </sst>
 </file>
@@ -962,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD27D292-CBD1-CA4F-A514-6D8CE062AE5E}">
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:M215"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="12.5" customWidth="1"/>
@@ -1376,7 +1382,7 @@
       <c r="H16" s="18"/>
       <c r="I16" s="19"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45215</v>
       </c>
@@ -1397,7 +1403,7 @@
       <c r="H17" s="18"/>
       <c r="I17" s="19"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45216</v>
       </c>
@@ -1426,7 +1432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45217</v>
       </c>
@@ -1455,7 +1461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45218</v>
       </c>
@@ -1484,7 +1490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>45219</v>
       </c>
@@ -1505,7 +1511,7 @@
       <c r="H21" s="17"/>
       <c r="I21" s="19"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>45220</v>
       </c>
@@ -1526,7 +1532,7 @@
       <c r="H22" s="17"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>45221</v>
       </c>
@@ -1547,7 +1553,7 @@
       <c r="H23" s="18"/>
       <c r="I23" s="19"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>45222</v>
       </c>
@@ -1568,7 +1574,7 @@
       <c r="H24" s="18"/>
       <c r="I24" s="19"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>45223</v>
       </c>
@@ -1589,7 +1595,7 @@
       <c r="H25" s="18"/>
       <c r="I25" s="19"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>45224</v>
       </c>
@@ -1614,11 +1620,14 @@
       <c r="H26" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="42" t="s">
+      <c r="I26" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="42" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>45225</v>
       </c>
@@ -1647,7 +1656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>45226</v>
       </c>
@@ -1676,7 +1685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>45227</v>
       </c>
@@ -1697,7 +1706,7 @@
       <c r="H29" s="17"/>
       <c r="I29" s="19"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>45228</v>
       </c>
@@ -1718,7 +1727,7 @@
       <c r="H30" s="18"/>
       <c r="I30" s="19"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>45229</v>
       </c>
@@ -1739,7 +1748,7 @@
       <c r="H31" s="18"/>
       <c r="I31" s="19"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>45230</v>
       </c>
@@ -1809,6 +1818,9 @@
       <c r="I34" s="43" t="s">
         <v>13</v>
       </c>
+      <c r="J34" s="42" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
@@ -2936,7 +2948,7 @@
       <c r="H80" s="18"/>
       <c r="I80" s="19"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>45279</v>
       </c>
@@ -2968,7 +2980,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>45280</v>
       </c>
@@ -3000,7 +3012,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>45281</v>
       </c>
@@ -3032,7 +3044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>45282</v>
       </c>
@@ -3053,7 +3065,7 @@
       <c r="H84" s="17"/>
       <c r="I84" s="19"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>45283</v>
       </c>
@@ -3074,7 +3086,7 @@
       <c r="H85" s="17"/>
       <c r="I85" s="19"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>45284</v>
       </c>
@@ -3095,7 +3107,7 @@
       <c r="H86" s="18"/>
       <c r="I86" s="19"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>45285</v>
       </c>
@@ -3116,7 +3128,7 @@
       <c r="H87" s="18"/>
       <c r="I87" s="19"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>45286</v>
       </c>
@@ -3137,7 +3149,7 @@
       <c r="H88" s="18"/>
       <c r="I88" s="19"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>45287</v>
       </c>
@@ -3166,7 +3178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>45288</v>
       </c>
@@ -3195,7 +3207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>45289</v>
       </c>
@@ -3220,14 +3232,17 @@
       <c r="H91" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I91" s="43" t="s">
-        <v>13</v>
+      <c r="I91" s="36" t="s">
+        <v>17</v>
       </c>
       <c r="J91" s="40" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="M91" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>45290</v>
       </c>
@@ -3248,7 +3263,7 @@
       <c r="H92" s="18"/>
       <c r="I92" s="19"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>45291</v>
       </c>
@@ -3269,7 +3284,7 @@
       <c r="H93" s="18"/>
       <c r="I93" s="19"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>45292</v>
       </c>
@@ -3290,7 +3305,7 @@
       <c r="H94" s="18"/>
       <c r="I94" s="19"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>45293</v>
       </c>
@@ -3311,7 +3326,7 @@
       <c r="H95" s="18"/>
       <c r="I95" s="19"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>45294</v>
       </c>
@@ -3750,8 +3765,8 @@
       <c r="H113" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I113" s="4" t="s">
-        <v>31</v>
+      <c r="I113" s="43" t="s">
+        <v>13</v>
       </c>
       <c r="J113" s="4" t="s">
         <v>31</v>
@@ -4446,7 +4461,10 @@
       <c r="H141" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I141" s="19" t="s">
+      <c r="I141" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J141" s="19" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4793,6 +4811,9 @@
       <c r="I154" s="43" t="s">
         <v>13</v>
       </c>
+      <c r="J154" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
@@ -4821,6 +4842,9 @@
       </c>
       <c r="I155" s="43" t="s">
         <v>13</v>
+      </c>
+      <c r="J155" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
@@ -4872,9 +4896,7 @@
       <c r="I157" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="J157" s="42" t="s">
-        <v>23</v>
-      </c>
+      <c r="J157" s="42"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
@@ -5315,7 +5337,7 @@
       <c r="H176" s="17"/>
       <c r="I176" s="19"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>45375</v>
       </c>
@@ -5344,7 +5366,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>45376</v>
       </c>
@@ -5373,7 +5395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>45377</v>
       </c>
@@ -5394,7 +5416,7 @@
       <c r="H179" s="17"/>
       <c r="I179" s="19"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>45378</v>
       </c>
@@ -5415,7 +5437,7 @@
       <c r="H180" s="17"/>
       <c r="I180" s="19"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>45379</v>
       </c>
@@ -5436,7 +5458,7 @@
       <c r="H181" s="17"/>
       <c r="I181" s="19"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>45380</v>
       </c>
@@ -5457,7 +5479,7 @@
       <c r="H182" s="17"/>
       <c r="I182" s="19"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>45381</v>
       </c>
@@ -5478,7 +5500,7 @@
       <c r="H183" s="17"/>
       <c r="I183" s="19"/>
     </row>
-    <row r="184" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="16">
         <v>45382</v>
       </c>
@@ -5507,7 +5529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="32" t="s">
         <v>10</v>
       </c>
@@ -5532,43 +5554,65 @@
         <v>69</v>
       </c>
       <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
+      <c r="H185">
+        <f>COUNTIF(H1:H184,"sent 1 month in advance")</f>
+        <v>31</v>
+      </c>
       <c r="I185">
         <f>COUNTIF(I1:I184,"True")</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="J185">
+        <f>COUNTIF(J1:J184,"human error")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H186">
+        <f>COUNTIF(H2:H185,"sent few days in advance")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H187" s="4">
+        <f>COUNTIF(H2:H185,"sent 1 day in advance")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F188" s="4"/>
       <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H188" s="4">
+        <f>COUNTIF(H3:H186,"sent 2 days in advance")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H189" s="4">
+        <f>COUNTIF(H4:H187,"sent 3 days in advance")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H190" s="4">
+        <f>SUM(H186:H189)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F191" s="10"/>
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F192" s="10"/>
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
@@ -5576,7 +5620,10 @@
     <row r="193" spans="6:8" x14ac:dyDescent="0.2">
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
+      <c r="H193" s="4">
+        <f>COUNTIF(H8:H191,"cating up a lost night ")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="194" spans="6:8" x14ac:dyDescent="0.2">
       <c r="F194" s="4"/>
